--- a/Dados/EEG_time.xlsx
+++ b/Dados/EEG_time.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidteixeira/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidteixeira/Documents/GitHub/DavidJMT/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57D240AF-981A-9A47-A8F5-658AD381FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD049E4-1F5D-AB4B-B19A-BE82B0626235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="500" windowWidth="28240" windowHeight="16120" xr2:uid="{62690E26-9F6E-D542-B320-2CBD81D7142D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28240" windowHeight="16120" xr2:uid="{62690E26-9F6E-D542-B320-2CBD81D7142D}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED80D2F-D32E-4845-8990-E3D110DFEBF4}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
@@ -544,6 +544,21 @@
         <v>45460.70957175926</v>
       </c>
     </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>45468.670138888891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>45468.717314814814</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>45471.659733796296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
